--- a/data/raw/LM2017.xlsx
+++ b/data/raw/LM2017.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAEC292C-B1CF-488E-8922-D856366BD8E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9140EEC0-A844-4E37-8652-3F5F3D92D1DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" tabRatio="913" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" tabRatio="913" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Introducción" sheetId="41" r:id="rId1"/>
@@ -26768,10 +26768,10 @@
         <v>67</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>0</v>
+        <v>572</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>1</v>
+        <v>573</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>59</v>

--- a/data/raw/LM2017.xlsx
+++ b/data/raw/LM2017.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9140EEC0-A844-4E37-8652-3F5F3D92D1DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B58CFD-0D0A-43D0-B932-272E17080C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" tabRatio="913" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" tabRatio="913" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Introducción" sheetId="41" r:id="rId1"/>
@@ -41,8 +41,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2591" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2579" uniqueCount="577">
   <si>
     <t>FONASA</t>
   </si>
@@ -1767,6 +1789,15 @@
   </si>
   <si>
     <t>isapre</t>
+  </si>
+  <si>
+    <t>hombre</t>
+  </si>
+  <si>
+    <t>mujer</t>
+  </si>
+  <si>
+    <t>sin_info</t>
   </si>
 </sst>
 </file>
@@ -35811,10 +35842,10 @@
         <v>208</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>0</v>
+        <v>572</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1</v>
+        <v>573</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>59</v>
@@ -36038,41 +36069,42 @@
       <c r="A23" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="B23" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="44" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="44" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="44" t="s">
-        <v>223</v>
-      </c>
-      <c r="H23" s="44" t="s">
-        <v>224</v>
-      </c>
-      <c r="I23" s="44" t="s">
-        <v>225</v>
-      </c>
-      <c r="J23" s="44" t="s">
-        <v>226</v>
-      </c>
-      <c r="K23" s="44" t="s">
-        <v>263</v>
-      </c>
-      <c r="L23" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="M23" s="44" t="s">
-        <v>478</v>
+      <c r="B23" s="44" t="str" cm="1">
+        <f t="array" ref="B23:M23">TRANSPOSE(A6:A17)</f>
+        <v>Trastornos mentales</v>
+      </c>
+      <c r="C23" s="44" t="str">
+        <v>Enf. osteomusculares</v>
+      </c>
+      <c r="D23" s="44" t="str">
+        <v>Enf. respiratorias</v>
+      </c>
+      <c r="E23" s="44" t="str">
+        <v>Traumatismos, envenenamientos y otros</v>
+      </c>
+      <c r="F23" s="44" t="str">
+        <v>Enf. infecciosas</v>
+      </c>
+      <c r="G23" s="44" t="str">
+        <v>Enf. del Sistema Digestivo</v>
+      </c>
+      <c r="H23" s="44" t="str">
+        <v>Afecciones del embarazo, Parto y Puerperio</v>
+      </c>
+      <c r="I23" s="44" t="str">
+        <v>Enfermedades del Sist. Genito urinario</v>
+      </c>
+      <c r="J23" s="44" t="str">
+        <v>Tumores y Cánceres</v>
+      </c>
+      <c r="K23" s="44" t="str">
+        <v>Enf. cardiovasculares</v>
+      </c>
+      <c r="L23" s="44" t="str">
+        <v>Otros diagnósticos</v>
+      </c>
+      <c r="M23" s="44" t="str">
+        <v>Sin información</v>
       </c>
       <c r="N23" s="44" t="s">
         <v>64</v>
@@ -36090,7 +36122,7 @@
         <v>11</v>
       </c>
       <c r="T23" s="44" t="s">
-        <v>12</v>
+        <v>480</v>
       </c>
       <c r="U23" s="44" t="s">
         <v>13</v>
@@ -36102,7 +36134,7 @@
         <v>224</v>
       </c>
       <c r="X23" s="44" t="s">
-        <v>225</v>
+        <v>481</v>
       </c>
       <c r="Y23" s="44" t="s">
         <v>226</v>
@@ -36122,7 +36154,7 @@
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A24" s="22" t="s">
-        <v>5</v>
+        <v>574</v>
       </c>
       <c r="B24" s="4">
         <v>199892</v>
@@ -36165,7 +36197,7 @@
       </c>
       <c r="O24" s="76"/>
       <c r="P24" s="22" t="s">
-        <v>5</v>
+        <v>574</v>
       </c>
       <c r="Q24" s="4">
         <v>97199.297897955796</v>
@@ -36210,7 +36242,7 @@
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A25" s="25" t="s">
-        <v>6</v>
+        <v>575</v>
       </c>
       <c r="B25" s="5">
         <v>611537</v>
@@ -36253,7 +36285,7 @@
       </c>
       <c r="O25" s="75"/>
       <c r="P25" s="25" t="s">
-        <v>6</v>
+        <v>575</v>
       </c>
       <c r="Q25" s="5">
         <v>140392.52656911677</v>
@@ -36298,7 +36330,7 @@
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A26" s="25" t="s">
-        <v>478</v>
+        <v>576</v>
       </c>
       <c r="B26" s="5">
         <v>0</v>
@@ -36341,7 +36373,7 @@
       </c>
       <c r="O26" s="75"/>
       <c r="P26" s="25" t="s">
-        <v>478</v>
+        <v>576</v>
       </c>
       <c r="Q26" s="5">
         <v>0</v>
@@ -36550,7 +36582,7 @@
         <v>11</v>
       </c>
       <c r="E32" s="44" t="s">
-        <v>12</v>
+        <v>480</v>
       </c>
       <c r="F32" s="44" t="s">
         <v>13</v>
@@ -36562,7 +36594,7 @@
         <v>224</v>
       </c>
       <c r="I32" s="44" t="s">
-        <v>225</v>
+        <v>481</v>
       </c>
       <c r="J32" s="44" t="s">
         <v>226</v>
@@ -36592,7 +36624,7 @@
         <v>11</v>
       </c>
       <c r="T32" s="44" t="s">
-        <v>12</v>
+        <v>480</v>
       </c>
       <c r="U32" s="44" t="s">
         <v>13</v>
@@ -36604,7 +36636,7 @@
         <v>224</v>
       </c>
       <c r="X32" s="44" t="s">
-        <v>225</v>
+        <v>481</v>
       </c>
       <c r="Y32" s="44" t="s">
         <v>226</v>
@@ -37492,7 +37524,7 @@
         <v>11</v>
       </c>
       <c r="E46" s="44" t="s">
-        <v>12</v>
+        <v>480</v>
       </c>
       <c r="F46" s="44" t="s">
         <v>13</v>
@@ -37504,7 +37536,7 @@
         <v>224</v>
       </c>
       <c r="I46" s="44" t="s">
-        <v>225</v>
+        <v>481</v>
       </c>
       <c r="J46" s="44" t="s">
         <v>226</v>
@@ -37534,7 +37566,7 @@
         <v>11</v>
       </c>
       <c r="T46" s="44" t="s">
-        <v>12</v>
+        <v>480</v>
       </c>
       <c r="U46" s="44" t="s">
         <v>13</v>
@@ -37546,7 +37578,7 @@
         <v>224</v>
       </c>
       <c r="X46" s="44" t="s">
-        <v>225</v>
+        <v>481</v>
       </c>
       <c r="Y46" s="44" t="s">
         <v>226</v>
